--- a/artfynd/A 11235-2025 artfynd.xlsx
+++ b/artfynd/A 11235-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120481227</v>
+        <v>120481228</v>
       </c>
       <c r="B2" t="n">
-        <v>94536</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318631</v>
+        <v>318676</v>
       </c>
       <c r="R2" t="n">
-        <v>6439101</v>
+        <v>6439062</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120481230</v>
+        <v>120481231</v>
       </c>
       <c r="B3" t="n">
-        <v>96999</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318685</v>
+        <v>318637</v>
       </c>
       <c r="R3" t="n">
-        <v>6439043</v>
+        <v>6439095</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120481228</v>
+        <v>120481225</v>
       </c>
       <c r="B4" t="n">
-        <v>94818</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>318676</v>
+        <v>318917</v>
       </c>
       <c r="R4" t="n">
-        <v>6439062</v>
+        <v>6438908</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +949,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Ucklum</t>
+          <t>Spekeröd</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120481231</v>
+        <v>120481227</v>
       </c>
       <c r="B5" t="n">
-        <v>96672</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>318637</v>
+        <v>318631</v>
       </c>
       <c r="R5" t="n">
-        <v>6439095</v>
+        <v>6439101</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,6 +1100,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120481230</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>318685</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6439043</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ucklum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
